--- a/downloads/ы.xlsx
+++ b/downloads/ы.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kules\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980A502B-7D6A-4AB1-B1C4-4E4F99370A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F9F9546-F147-47F3-8E71-A42328C804A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{6343E0CB-D9F8-4BF1-83B0-A71A41BD33F9}"/>
+    <workbookView xWindow="4875" yWindow="3825" windowWidth="28800" windowHeight="15885" xr2:uid="{6343E0CB-D9F8-4BF1-83B0-A71A41BD33F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="47">
   <si>
     <t>время</t>
   </si>
@@ -114,10 +114,70 @@
     <t>13.10-13.50</t>
   </si>
   <si>
-    <t>MATH</t>
-  </si>
-  <si>
-    <t>RUSSIAN</t>
+    <t>РОВ</t>
+  </si>
+  <si>
+    <t>Русский Яз.</t>
+  </si>
+  <si>
+    <t>Англ Яз.</t>
+  </si>
+  <si>
+    <t>История</t>
+  </si>
+  <si>
+    <t>ИЗО</t>
+  </si>
+  <si>
+    <t>математика</t>
+  </si>
+  <si>
+    <t>Русский</t>
+  </si>
+  <si>
+    <t>География</t>
+  </si>
+  <si>
+    <t>Анлиский</t>
+  </si>
+  <si>
+    <t>Математика</t>
+  </si>
+  <si>
+    <t>Англисский</t>
+  </si>
+  <si>
+    <t>Физика</t>
+  </si>
+  <si>
+    <t>Алгебра</t>
+  </si>
+  <si>
+    <t>Литиратура</t>
+  </si>
+  <si>
+    <t>Англиский</t>
+  </si>
+  <si>
+    <t>Музыка</t>
+  </si>
+  <si>
+    <t>Биология</t>
+  </si>
+  <si>
+    <t>Химия</t>
+  </si>
+  <si>
+    <t>Англиссикй</t>
+  </si>
+  <si>
+    <t>ИВТ_Англ</t>
+  </si>
+  <si>
+    <t>ИВТ</t>
+  </si>
+  <si>
+    <t>Общество</t>
   </si>
 </sst>
 </file>
@@ -173,7 +233,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -384,16 +444,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -409,39 +496,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -449,6 +518,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -774,109 +846,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10">
-        <v>45923</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="6"/>
+      <c r="A1" s="12">
+        <v>45928</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="14"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="9"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="17"/>
     </row>
     <row r="3" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="12" t="s">
+      <c r="O3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="12" t="s">
+      <c r="R3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="22" t="s">
+      <c r="S3" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="18">
         <v>1</v>
       </c>
       <c r="C4" s="23" t="s">
@@ -910,7 +982,7 @@
         <v>25</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>25</v>
@@ -925,660 +997,660 @@
         <v>25</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="S4" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="19"/>
       <c r="C5" s="24"/>
       <c r="D5" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1">
+        <v>26</v>
+      </c>
+      <c r="G5" s="1">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1">
+        <v>15</v>
+      </c>
+      <c r="I5" s="1">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1">
+        <v>29</v>
+      </c>
+      <c r="K5" s="1">
+        <v>28</v>
+      </c>
+      <c r="L5" s="1">
+        <v>28</v>
+      </c>
+      <c r="M5" s="1">
+        <v>12</v>
+      </c>
+      <c r="N5" s="1">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1">
+        <v>24</v>
+      </c>
+      <c r="P5" s="1">
+        <v>17</v>
+      </c>
+      <c r="Q5" s="1">
         <v>11</v>
       </c>
-      <c r="F5" s="1">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1">
-        <v>13</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="R5" s="1">
+        <v>16</v>
+      </c>
+      <c r="S5" s="1">
         <v>14</v>
-      </c>
-      <c r="I5" s="1">
-        <v>15</v>
-      </c>
-      <c r="J5" s="1">
-        <v>16</v>
-      </c>
-      <c r="K5" s="1">
-        <v>17</v>
-      </c>
-      <c r="L5" s="1">
-        <v>18</v>
-      </c>
-      <c r="M5" s="1">
-        <v>19</v>
-      </c>
-      <c r="N5" s="1">
-        <v>20</v>
-      </c>
-      <c r="O5" s="1">
-        <v>21</v>
-      </c>
-      <c r="P5" s="1">
-        <v>22</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>23</v>
-      </c>
-      <c r="R5" s="1">
-        <v>24</v>
-      </c>
-      <c r="S5" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="19">
+      <c r="A6" s="10"/>
+      <c r="B6" s="22">
         <v>2</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="26" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>26</v>
+      <c r="E6" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="21"/>
       <c r="D7" s="4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E7" s="4">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1">
+        <v>18</v>
+      </c>
+      <c r="H7" s="4">
+        <v>11</v>
+      </c>
+      <c r="I7" s="4">
+        <v>20</v>
+      </c>
+      <c r="J7" s="4">
+        <v>26</v>
+      </c>
+      <c r="K7" s="4">
+        <v>14</v>
+      </c>
+      <c r="L7" s="4">
+        <v>28</v>
+      </c>
+      <c r="M7" s="4">
+        <v>30</v>
+      </c>
+      <c r="N7" s="4">
         <v>24</v>
       </c>
-      <c r="F7" s="4">
-        <v>25</v>
-      </c>
-      <c r="G7" s="4">
-        <v>26</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="O7" s="4">
+        <v>25</v>
+      </c>
+      <c r="P7" s="4">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>2322</v>
+      </c>
+      <c r="R7" s="4">
         <v>27</v>
       </c>
-      <c r="I7" s="4">
-        <v>28</v>
-      </c>
-      <c r="J7" s="4">
-        <v>29</v>
-      </c>
-      <c r="K7" s="4">
-        <v>30</v>
-      </c>
-      <c r="L7" s="4">
-        <v>31</v>
-      </c>
-      <c r="M7" s="4">
-        <v>32</v>
-      </c>
-      <c r="N7" s="4">
-        <v>33</v>
-      </c>
-      <c r="O7" s="4">
-        <v>34</v>
-      </c>
-      <c r="P7" s="4">
-        <v>35</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>36</v>
-      </c>
-      <c r="R7" s="4">
-        <v>37</v>
-      </c>
       <c r="S7" s="4">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="14">
+      <c r="A8" s="10"/>
+      <c r="B8" s="18">
         <v>3</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="20" t="s">
         <v>20</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="18"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="1">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1">
+        <v>18</v>
+      </c>
+      <c r="G9" s="1">
+        <v>12</v>
+      </c>
+      <c r="H9" s="4">
+        <v>28</v>
+      </c>
+      <c r="I9" s="4">
+        <v>20</v>
+      </c>
+      <c r="J9" s="1">
+        <v>11</v>
+      </c>
+      <c r="K9" s="1">
+        <v>21</v>
+      </c>
+      <c r="L9" s="1">
+        <v>16</v>
+      </c>
+      <c r="M9" s="1">
         <v>10</v>
       </c>
-      <c r="E9" s="1">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1">
-        <v>12</v>
-      </c>
-      <c r="G9" s="1">
-        <v>13</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="N9" s="1">
+        <v>19</v>
+      </c>
+      <c r="O9" s="4">
+        <v>24</v>
+      </c>
+      <c r="P9" s="1">
         <v>14</v>
       </c>
-      <c r="I9" s="1">
-        <v>15</v>
-      </c>
-      <c r="J9" s="1">
-        <v>16</v>
-      </c>
-      <c r="K9" s="1">
-        <v>17</v>
-      </c>
-      <c r="L9" s="1">
-        <v>18</v>
-      </c>
-      <c r="M9" s="1">
-        <v>19</v>
-      </c>
-      <c r="N9" s="1">
-        <v>20</v>
-      </c>
-      <c r="O9" s="1">
-        <v>21</v>
-      </c>
-      <c r="P9" s="1">
-        <v>22</v>
-      </c>
       <c r="Q9" s="1">
-        <v>23</v>
+        <v>2322</v>
       </c>
       <c r="R9" s="1">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S9" s="1">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="19">
+      <c r="A10" s="10"/>
+      <c r="B10" s="22">
         <v>4</v>
       </c>
       <c r="C10" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="24"/>
       <c r="D11" s="4">
-        <v>23</v>
-      </c>
-      <c r="E11" s="4">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1">
+        <v>18</v>
+      </c>
+      <c r="F11" s="4">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4">
+        <v>29</v>
+      </c>
+      <c r="H11" s="4">
+        <v>16</v>
+      </c>
+      <c r="I11" s="4">
+        <v>11</v>
+      </c>
+      <c r="J11" s="4">
+        <v>20</v>
+      </c>
+      <c r="K11" s="4">
+        <v>28</v>
+      </c>
+      <c r="L11" s="1">
+        <v>21</v>
+      </c>
+      <c r="M11" s="4">
+        <v>26</v>
+      </c>
+      <c r="N11" s="4">
+        <v>27</v>
+      </c>
+      <c r="O11" s="4">
+        <v>10</v>
+      </c>
+      <c r="P11" s="4">
         <v>24</v>
       </c>
-      <c r="F11" s="4">
-        <v>25</v>
-      </c>
-      <c r="G11" s="4">
-        <v>26</v>
-      </c>
-      <c r="H11" s="4">
-        <v>27</v>
-      </c>
-      <c r="I11" s="4">
-        <v>28</v>
-      </c>
-      <c r="J11" s="4">
-        <v>29</v>
-      </c>
-      <c r="K11" s="4">
-        <v>30</v>
-      </c>
-      <c r="L11" s="4">
-        <v>31</v>
-      </c>
-      <c r="M11" s="4">
-        <v>32</v>
-      </c>
-      <c r="N11" s="4">
-        <v>33</v>
-      </c>
-      <c r="O11" s="4">
-        <v>34</v>
-      </c>
-      <c r="P11" s="4">
-        <v>35</v>
-      </c>
       <c r="Q11" s="4">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="R11" s="4">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S11" s="4">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="14">
+      <c r="A12" s="10"/>
+      <c r="B12" s="18">
         <v>5</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="19"/>
       <c r="C13" s="25"/>
       <c r="D13" s="1">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>19</v>
+      </c>
+      <c r="I13" s="1">
+        <v>28</v>
+      </c>
+      <c r="J13" s="4">
+        <v>20</v>
+      </c>
+      <c r="K13" s="1">
+        <v>16</v>
+      </c>
+      <c r="L13" s="1">
+        <v>21</v>
+      </c>
+      <c r="M13" s="1">
+        <v>14</v>
+      </c>
+      <c r="N13" s="1">
         <v>10</v>
       </c>
-      <c r="E13" s="1">
+      <c r="O13" s="1">
+        <v>12</v>
+      </c>
+      <c r="P13" s="1">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>24</v>
+      </c>
+      <c r="R13" s="1">
+        <v>23</v>
+      </c>
+      <c r="S13" s="1">
         <v>11</v>
-      </c>
-      <c r="F13" s="1">
-        <v>12</v>
-      </c>
-      <c r="G13" s="1">
-        <v>13</v>
-      </c>
-      <c r="H13" s="1">
-        <v>14</v>
-      </c>
-      <c r="I13" s="1">
-        <v>15</v>
-      </c>
-      <c r="J13" s="1">
-        <v>16</v>
-      </c>
-      <c r="K13" s="1">
-        <v>17</v>
-      </c>
-      <c r="L13" s="1">
-        <v>18</v>
-      </c>
-      <c r="M13" s="1">
-        <v>19</v>
-      </c>
-      <c r="N13" s="1">
-        <v>20</v>
-      </c>
-      <c r="O13" s="1">
-        <v>21</v>
-      </c>
-      <c r="P13" s="1">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>23</v>
-      </c>
-      <c r="R13" s="1">
-        <v>24</v>
-      </c>
-      <c r="S13" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="19">
+      <c r="A14" s="10"/>
+      <c r="B14" s="22">
         <v>6</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
+      <c r="D14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="15" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="24"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
+      <c r="D15" s="4">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4">
+        <v>21</v>
+      </c>
+      <c r="H15" s="4">
+        <v>15</v>
+      </c>
+      <c r="I15" s="4">
+        <v>26</v>
+      </c>
+      <c r="J15" s="4">
+        <v>28</v>
+      </c>
+      <c r="K15" s="4">
+        <v>18</v>
+      </c>
+      <c r="L15" s="4">
+        <v>14</v>
+      </c>
+      <c r="M15" s="4">
+        <v>20</v>
+      </c>
+      <c r="N15" s="4">
+        <v>25</v>
+      </c>
+      <c r="O15" s="4">
+        <v>27</v>
+      </c>
+      <c r="P15" s="4">
+        <v>2322</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>19</v>
+      </c>
+      <c r="R15" s="4">
+        <v>24</v>
+      </c>
+      <c r="S15" s="4">
+        <v>11</v>
+      </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="14">
+      <c r="A16" s="10"/>
+      <c r="B16" s="18">
         <v>7</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
     </row>
     <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="4">
-        <v>23</v>
-      </c>
-      <c r="E17" s="4">
-        <v>24</v>
-      </c>
-      <c r="F17" s="4">
-        <v>25</v>
-      </c>
-      <c r="G17" s="4">
-        <v>26</v>
-      </c>
-      <c r="H17" s="4">
-        <v>27</v>
-      </c>
-      <c r="I17" s="4">
-        <v>28</v>
-      </c>
-      <c r="J17" s="4">
-        <v>29</v>
-      </c>
-      <c r="K17" s="4">
-        <v>30</v>
-      </c>
-      <c r="L17" s="4">
-        <v>31</v>
-      </c>
-      <c r="M17" s="4">
-        <v>32</v>
-      </c>
-      <c r="N17" s="4">
-        <v>33</v>
-      </c>
-      <c r="O17" s="4">
-        <v>34</v>
-      </c>
-      <c r="P17" s="4">
-        <v>35</v>
-      </c>
-      <c r="Q17" s="4">
-        <v>36</v>
-      </c>
-      <c r="R17" s="4">
-        <v>37</v>
-      </c>
-      <c r="S17" s="4">
-        <v>38</v>
-      </c>
+      <c r="A17" s="11"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="16">
